--- a/products/mlcc/hv-mlcc-data.xlsx
+++ b/products/mlcc/hv-mlcc-data.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58804537-7CA1-408B-8816-6F4AB9983439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maxgain-my.sharepoint.com/personal/kwonik_maxgain_onmicrosoft_com/Documents/MAXGAIN SYSTEMS/MAXGAIN SYSTEMS/세라닉스/홈페이지/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{58804537-7CA1-408B-8816-6F4AB9983439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1022FC69-5F68-40A6-A3FD-D2F24295E12C}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17268" yWindow="1524" windowWidth="16416" windowHeight="13116" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="86">
   <si>
     <t>PartNumber</t>
   </si>
@@ -82,9 +87,6 @@
   </si>
   <si>
     <t>100pF</t>
-  </si>
-  <si>
-    <t>확인 필요</t>
   </si>
   <si>
     <t>NPO</t>
@@ -301,7 +303,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -315,6 +317,12 @@
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -367,14 +375,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProductsTable" displayName="ProductsTable" ref="A1:K16">
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProductsTable" displayName="ProductsTable" ref="A1:J16">
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PartNumber"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Series"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Package"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Voltage"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Capacitance"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Temperature"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Dielectric"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Tolerance"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Remark"/>
@@ -551,21 +558,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,25 +588,22 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -625,16 +628,13 @@
       <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -646,7 +646,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -657,16 +657,13 @@
       <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -675,7 +672,7 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -689,16 +686,13 @@
       <c r="H4" t="s">
         <v>18</v>
       </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -710,27 +704,24 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
         <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
       </c>
       <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
         <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -742,27 +733,24 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -774,27 +762,24 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -803,170 +788,155 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>37</v>
       </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
       <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
         <v>26</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
         <v>39</v>
       </c>
-      <c r="K9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" t="s">
-        <v>39</v>
-      </c>
-      <c r="K10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
         <v>26</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
         <v>44</v>
       </c>
-      <c r="E12" t="s">
-        <v>45</v>
-      </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G12" t="s">
         <v>27</v>
       </c>
       <c r="H12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -977,110 +947,99 @@
       <c r="H13" t="s">
         <v>18</v>
       </c>
-      <c r="I13" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="J13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
         <v>26</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
       </c>
       <c r="G14" t="s">
         <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G15" t="s">
         <v>27</v>
       </c>
       <c r="H15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
         <v>53</v>
       </c>
-      <c r="D16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" t="s">
-        <v>54</v>
-      </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G16" t="s">
         <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1092,7 +1051,7 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K500</xm:sqref>
+          <xm:sqref>J2:J500</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1103,7 +1062,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1118,28 +1077,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>10</v>
@@ -1151,16 +1110,16 @@
         <v/>
       </c>
       <c r="E2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
         <v>63</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>64</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>65</v>
-      </c>
-      <c r="I2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1169,19 +1128,20 @@
         <v/>
       </c>
       <c r="E3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" t="s">
         <v>67</v>
       </c>
-      <c r="G3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" t="s">
-        <v>68</v>
-      </c>
       <c r="I3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1216,40 +1176,40 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="27.6">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
         <v>72</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
         <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1257,34 +1217,35 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
         <v>77</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
         <v>79</v>
-      </c>
-      <c r="B7" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
         <v>81</v>
       </c>
-      <c r="B8" t="s">
-        <v>82</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1292,7 +1253,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
   </cols>
@@ -1302,46 +1263,47 @@
         <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
         <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
         <v>84</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>85</v>
       </c>
-      <c r="C4" t="s">
-        <v>86</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>